--- a/tools/config/quality.xlsx
+++ b/tools/config/quality.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -527,6 +527,16 @@
           <t>min_item_level</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>affix_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>has_aspect</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -552,6 +562,16 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bool</t>
         </is>
       </c>
     </row>
@@ -565,6 +585,8 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr"/>
@@ -580,6 +602,8 @@
       </c>
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -605,6 +629,16 @@
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>该品质最低物品等级</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>随机词缀数量</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>是否携带威能</t>
         </is>
       </c>
     </row>
@@ -628,6 +662,12 @@
       <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -649,6 +689,12 @@
       <c r="E7" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -670,6 +716,12 @@
       <c r="E8" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -691,6 +743,12 @@
       <c r="E9" s="7" t="n">
         <v>15</v>
       </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -711,6 +769,12 @@
       </c>
       <c r="E10" s="6" t="n">
         <v>20</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
